--- a/docs/package/05_Delivery/Upload_Templates/Endorsement_Insurer_Commission_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Endorsement_Insurer_Commission_Template.xlsx
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Upload on</t>
   </si>
   <si>
-    <t xml:space="preserve">Operations &gt; Policy &gt; Endorsement &gt; Upload insurer commission</t>
+    <t xml:space="preserve">Policy Servicing &gt; Policy &gt; Endorsement &gt; Upload insurer commission</t>
   </si>
   <si>
     <t xml:space="preserve">File types</t>
